--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdcr2613\Desktop\BS_PD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssamu\Desktop\Coding\alas-catalogo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B966A39E-4A24-477F-8BE2-105955C5D3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1043F075-EEE4-4D3C-A29F-67A9D99C60ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="136">
   <si>
     <t>Product Image</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>Inspirado en la serenidad del mar, este anillo captura la esencia de lo natural con un diseño orgánico y elegante que evoca calma y libertad. \n\n**Cuidados**: Evitar agua salada y químicos. Limpiar con paño seco.</t>
+  </si>
+  <si>
+    <t>Anillo Curvas Abstractas</t>
   </si>
 </sst>
 </file>
@@ -3199,7 +3202,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3515,16 +3518,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A0122F-59D4-4637-BE6F-DD49479A8C39}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="3" customWidth="1"/>
-    <col min="4" max="11" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="3" customWidth="1"/>
+    <col min="4" max="11" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3559,7 +3563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3594,7 +3598,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -3629,7 +3633,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -3664,7 +3668,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -3699,7 +3703,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3734,7 +3738,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3769,7 +3773,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -3804,7 +3808,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -3839,7 +3843,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3874,7 +3878,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -3909,7 +3913,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3944,7 +3948,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3979,7 +3983,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4014,7 +4018,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -4049,7 +4053,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -4084,7 +4088,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -4119,7 +4123,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -4154,7 +4158,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -4189,7 +4193,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -4224,7 +4228,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -4259,7 +4263,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -4294,7 +4298,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -4329,7 +4333,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
@@ -4364,7 +4368,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
@@ -4399,9 +4403,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>56</v>
@@ -4434,7 +4438,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
@@ -4469,7 +4473,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -4504,7 +4508,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -4539,7 +4543,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -4574,7 +4578,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -4609,7 +4613,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -4679,7 +4683,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -4714,7 +4718,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -4749,7 +4753,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -4784,7 +4788,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -4820,7 +4824,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}"/>
+  <autoFilter ref="A1:K37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Anillo Corazón Asimétrico"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -4829,17 +4839,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A83E87-90D2-4FFE-A6A7-E278883B4F92}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
-    <col min="5" max="12" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
+    <col min="5" max="12" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4877,7 +4888,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4913,7 +4924,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4949,7 +4960,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -4985,7 +4996,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -5021,7 +5032,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -5057,7 +5068,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -5093,7 +5104,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -5129,7 +5140,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -5165,7 +5176,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -5201,7 +5212,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -5237,7 +5248,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -5273,7 +5284,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -5309,7 +5320,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -5345,7 +5356,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -5381,7 +5392,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -5417,7 +5428,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -5453,7 +5464,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -5489,7 +5500,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
@@ -5525,7 +5536,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
@@ -5597,7 +5608,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>1</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
@@ -5669,7 +5680,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>1</v>
       </c>
@@ -5705,7 +5716,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
@@ -5741,7 +5752,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -5813,7 +5824,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -5849,7 +5860,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -5885,7 +5896,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
@@ -5921,7 +5932,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
@@ -5957,7 +5968,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -5993,7 +6004,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -6029,7 +6040,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -6065,7 +6076,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -6101,7 +6112,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
@@ -6137,7 +6148,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -6173,17 +6184,23 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:L37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}"/>
+  <autoFilter ref="A1:L37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Anillo Corazón Asimétrico"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssamu\Desktop\Coding\alas-catalogo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1043F075-EEE4-4D3C-A29F-67A9D99C60ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EB2422-06EB-4577-BA1B-7F00D7C1E553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="5" r:id="rId1"/>
@@ -3518,17 +3518,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A0122F-59D4-4637-BE6F-DD49479A8C39}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="3" customWidth="1"/>
-    <col min="4" max="11" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="3" customWidth="1"/>
+    <col min="4" max="11" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3563,7 +3562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -3668,7 +3667,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -3703,7 +3702,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3738,7 +3737,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3773,7 +3772,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -3808,7 +3807,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -3843,7 +3842,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3878,7 +3877,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -3913,7 +3912,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3948,7 +3947,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4018,7 +4017,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -4053,7 +4052,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -4088,7 +4087,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -4123,7 +4122,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -4158,7 +4157,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -4193,7 +4192,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -4228,7 +4227,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -4263,7 +4262,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -4298,7 +4297,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -4333,7 +4332,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
@@ -4368,7 +4367,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
@@ -4403,7 +4402,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>135</v>
       </c>
@@ -4438,7 +4437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -4508,7 +4507,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -4543,7 +4542,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -4578,7 +4577,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -4648,7 +4647,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -4683,7 +4682,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -4824,13 +4823,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Anillo Corazón Asimétrico"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -4841,16 +4834,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A83E87-90D2-4FFE-A6A7-E278883B4F92}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
-    <col min="5" max="12" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
+    <col min="5" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4888,7 +4881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4924,7 +4917,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4960,7 +4953,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -4996,7 +4989,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -5032,7 +5025,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -5068,7 +5061,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -5104,7 +5097,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -5140,7 +5133,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -5176,7 +5169,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -5212,7 +5205,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -5248,7 +5241,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -5284,7 +5277,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -5320,7 +5313,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -5356,7 +5349,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -5392,7 +5385,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -5428,7 +5421,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -5464,7 +5457,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -5500,7 +5493,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
@@ -5536,7 +5529,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -5572,7 +5565,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
@@ -5608,7 +5601,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>1</v>
       </c>
@@ -5644,7 +5637,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
@@ -5680,7 +5673,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>1</v>
       </c>
@@ -5716,7 +5709,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
@@ -5752,7 +5745,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -5788,7 +5781,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -5824,7 +5817,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -5860,7 +5853,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -5896,7 +5889,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
@@ -5932,7 +5925,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
@@ -5968,7 +5961,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -6004,7 +5997,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -6040,7 +6033,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -6076,7 +6069,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -6112,7 +6105,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
@@ -6148,7 +6141,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -6184,15 +6177,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:L37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}">
     <filterColumn colId="1">

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssamu\Desktop\Coding\alas-catalogo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EB2422-06EB-4577-BA1B-7F00D7C1E553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C495729A-4A31-4D66-ADC2-09053E8B50DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="176">
   <si>
     <t>Product Image</t>
   </si>
@@ -446,6 +446,126 @@
   </si>
   <si>
     <t>Anillo Curvas Abstractas</t>
+  </si>
+  <si>
+    <t>Aretes Corazon Chunky</t>
+  </si>
+  <si>
+    <t>Aretes Set Constelaciones</t>
+  </si>
+  <si>
+    <t>Aretes Espiral</t>
+  </si>
+  <si>
+    <t>Aretes Cherry</t>
+  </si>
+  <si>
+    <t>Aretes Flor Colgante</t>
+  </si>
+  <si>
+    <t>Aretes Trio Corazones</t>
+  </si>
+  <si>
+    <t>Aretes Monarca</t>
+  </si>
+  <si>
+    <t>Pulsera Paper Clip</t>
+  </si>
+  <si>
+    <t>Brazalete Corazón Hueco</t>
+  </si>
+  <si>
+    <t>Brazalete Chunk</t>
+  </si>
+  <si>
+    <t>Pulsera Tenis Tres Corazones</t>
+  </si>
+  <si>
+    <t>Collar 11:11</t>
+  </si>
+  <si>
+    <t>Collar Hilo Negro</t>
+  </si>
+  <si>
+    <t>Aretes dorados con diseño de corazón chunky.</t>
+  </si>
+  <si>
+    <t>Set de 6 aretes con variedad, ideal si usas varios en cada oreja, estilo estrellas, luna y destellos.</t>
+  </si>
+  <si>
+    <t>Aretes dorados con forma de espiral.</t>
+  </si>
+  <si>
+    <t>Aretes dorados con diseño de cereza colgando.</t>
+  </si>
+  <si>
+    <t>Aretes dorados con diseño de flor.</t>
+  </si>
+  <si>
+    <t>Aretes dorados colgantes, con diseño de 3 corazones en cadena.</t>
+  </si>
+  <si>
+    <t>Aretes dorados con diseño de lluvia dorada.</t>
+  </si>
+  <si>
+    <t>Pulsera dorada paperclip. Se le puede colocar dijes personalizados.</t>
+  </si>
+  <si>
+    <t>Brazalete dorado con detalle de corazón.</t>
+  </si>
+  <si>
+    <t>Brazalete dorado estilo chunk.</t>
+  </si>
+  <si>
+    <t>Pulsera dorada tenis con 3 corazones de zirconia.</t>
+  </si>
+  <si>
+    <t>Collar 11:11 dorado delicado, pide tu deseo.</t>
+  </si>
+  <si>
+    <t>Collar de hilo negro, con estilo para colocar alrededor del cuello.</t>
+  </si>
+  <si>
+    <t>PVD Baño de Oro 18K, Rodio</t>
+  </si>
+  <si>
+    <t>Un diseño moderno para toda ocasión, confiables para tu día a día, pero también muestran un estilo moderno que te hace destacar. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Estos aretes imitan el brillo de los astros. Con este bonito diseño tendrás todo para destacar con sus destellos. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Un diseño que imita una espiral, resalta tu estilo con estos aretes con mucha personalidad. Atrévete a darle un toque diferente a tu outfit. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Estos aretes gritan personalidad, eleva tu estilo dandole un toque de color rojo con muchas seguridad. Con estos serás el centro de atención. Para ocasiones semiformales donde quieres destacar. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Este diseño elegante para ocasiones especiales no pasa de moda. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Complementa tu vestido con estos aretes de corazón. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>La elegancia cobra una nueva definición con los aretes monarca. Su brillo acompaña ocasiones especiales. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Dale un toque de personalidad a tu diario. Esta pulsera permite colocar dijes personalizados. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Para toda ocasión donde quieras accesorizar tu outfit, este brazalete encaja perfecto. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Complemente con tus pulseras y brazaletes, con este brazalete lleno de personalidad. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Pulsera tenis con 3 corazones muy linda y perfecta para regalar. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Pide tu deseo 11:11. Lo que más anhela tu corazón será cumplido. Con este collar viral. \n\nCuidados: Evitar perfumes y humedad.</t>
+  </si>
+  <si>
+    <t>Dale un estilo diferente a tu outfit con este collar para colocar alrededor del cuello. Desde vestidos elegantes hasta combinaciones casuales. \n\nCuidados: Evitar perfumes y humedad.</t>
   </si>
 </sst>
 </file>
@@ -476,7 +596,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -499,11 +619,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -515,11 +646,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3518,16 +3663,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A0122F-59D4-4637-BE6F-DD49479A8C39}">
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="3" customWidth="1"/>
-    <col min="4" max="11" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="3" customWidth="1"/>
+    <col min="4" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="255.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3562,18 +3708,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
-        <v>13.99</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>16.989999999999998</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>132</v>
@@ -3582,33 +3728,33 @@
         <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J2" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2">
-        <v>13.99</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>16.989999999999998</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>132</v>
@@ -3617,33 +3763,33 @@
         <v>88</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J3" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2">
         <v>14.99</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>90</v>
+      <c r="D4" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>132</v>
@@ -3652,7 +3798,7 @@
         <v>88</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>87</v>
@@ -3661,24 +3807,24 @@
         <v>88</v>
       </c>
       <c r="J4" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>14.99</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>132</v>
@@ -3687,33 +3833,33 @@
         <v>88</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J5" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C6" s="2">
-        <v>4.99</v>
+        <v>14.99</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>132</v>
@@ -3731,24 +3877,24 @@
         <v>88</v>
       </c>
       <c r="J6" s="1">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2">
-        <v>4.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>132</v>
@@ -3766,21 +3912,21 @@
         <v>88</v>
       </c>
       <c r="J7" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2">
-        <v>14.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>92</v>
@@ -3792,33 +3938,33 @@
         <v>88</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J8" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -3836,24 +3982,24 @@
         <v>88</v>
       </c>
       <c r="J9" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C10" s="2">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>132</v>
@@ -3862,33 +4008,33 @@
         <v>88</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J10" s="1">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C11" s="2">
-        <v>16.989999999999998</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>132</v>
@@ -3897,33 +4043,33 @@
         <v>88</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2">
-        <v>16.989999999999998</v>
+        <v>11.99</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>132</v>
@@ -3932,33 +4078,33 @@
         <v>88</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J12" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C13" s="2">
         <v>14.99</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>89</v>
+      <c r="D13" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>132</v>
@@ -3976,24 +4122,24 @@
         <v>88</v>
       </c>
       <c r="J13" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C14" s="2">
         <v>14.99</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>89</v>
+      <c r="D14" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>132</v>
@@ -4002,7 +4148,7 @@
         <v>88</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>87</v>
@@ -4011,24 +4157,24 @@
         <v>88</v>
       </c>
       <c r="J14" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2">
-        <v>12.99</v>
+        <v>14.99</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>132</v>
@@ -4037,27 +4183,27 @@
         <v>88</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J15" s="1">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2">
         <v>4.99</v>
@@ -4072,33 +4218,33 @@
         <v>88</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J16" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2">
-        <v>14.99</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>89</v>
+        <v>4.99</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>132</v>
@@ -4107,33 +4253,33 @@
         <v>88</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J17" s="1">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2">
-        <v>4.99</v>
+        <v>14.99</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>132</v>
@@ -4142,7 +4288,7 @@
         <v>88</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>87</v>
@@ -4151,24 +4297,24 @@
         <v>88</v>
       </c>
       <c r="J18" s="1">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2">
-        <v>19.989999999999998</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>91</v>
+        <v>13.99</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>132</v>
@@ -4177,33 +4323,33 @@
         <v>88</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J19" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2">
-        <v>4.99</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>13.99</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>132</v>
@@ -4212,33 +4358,33 @@
         <v>88</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J20" s="1">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C21" s="2">
-        <v>14.99</v>
+        <v>4.99</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>132</v>
@@ -4256,24 +4402,24 @@
         <v>88</v>
       </c>
       <c r="J21" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2">
-        <v>14.99</v>
+        <v>4.99</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>132</v>
@@ -4282,33 +4428,33 @@
         <v>88</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J22" s="1">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>14.99</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>132</v>
@@ -4317,7 +4463,7 @@
         <v>88</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>87</v>
@@ -4326,24 +4472,24 @@
         <v>88</v>
       </c>
       <c r="J23" s="1">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2">
-        <v>16.989999999999998</v>
+        <v>12.99</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>132</v>
@@ -4352,33 +4498,33 @@
         <v>88</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J24" s="1">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>13.99</v>
+        <v>4.99</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>132</v>
@@ -4387,33 +4533,33 @@
         <v>88</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J25" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2">
-        <v>4.99</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>91</v>
+        <v>14.99</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>132</v>
@@ -4422,7 +4568,7 @@
         <v>88</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>87</v>
@@ -4431,24 +4577,24 @@
         <v>88</v>
       </c>
       <c r="J26" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2">
-        <v>12.99</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>89</v>
+        <v>4.99</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>132</v>
@@ -4466,24 +4612,24 @@
         <v>88</v>
       </c>
       <c r="J27" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
-        <v>14.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>132</v>
@@ -4492,7 +4638,7 @@
         <v>88</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>86</v>
@@ -4501,24 +4647,24 @@
         <v>88</v>
       </c>
       <c r="J28" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C29" s="2">
-        <v>14.99</v>
+        <v>4.99</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>132</v>
@@ -4527,7 +4673,7 @@
         <v>88</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>87</v>
@@ -4536,24 +4682,24 @@
         <v>88</v>
       </c>
       <c r="J29" s="1">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>132</v>
@@ -4562,33 +4708,33 @@
         <v>88</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J30" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>132</v>
@@ -4606,24 +4752,24 @@
         <v>88</v>
       </c>
       <c r="J31" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2">
-        <v>4.99</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>91</v>
+        <v>12.99</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>132</v>
@@ -4641,24 +4787,24 @@
         <v>88</v>
       </c>
       <c r="J32" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>132</v>
@@ -4667,33 +4813,33 @@
         <v>88</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J33" s="1">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>132</v>
@@ -4702,33 +4848,33 @@
         <v>88</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J34" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>132</v>
@@ -4737,7 +4883,7 @@
         <v>88</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>87</v>
@@ -4746,24 +4892,24 @@
         <v>88</v>
       </c>
       <c r="J35" s="1">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
-        <v>19.989999999999998</v>
+        <v>9.99</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>132</v>
@@ -4772,33 +4918,33 @@
         <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>88</v>
       </c>
       <c r="J36" s="1">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C37" s="2">
-        <v>14.99</v>
+        <v>9.99</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>132</v>
@@ -4807,23 +4953,488 @@
         <v>88</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J37" s="1">
+        <v>36</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="2">
+        <v>14.99</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J37" s="1">
-        <v>12</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="I38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J38" s="5">
+        <v>37</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="2">
+        <v>24.99</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J39" s="1">
+        <v>38</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="2">
+        <v>14.99</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" t="s">
+        <v>162</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J40" s="5">
+        <v>39</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="2">
+        <v>14.99</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" t="s">
+        <v>162</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J41" s="1">
+        <v>40</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="2">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J42" s="5">
+        <v>41</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="2">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J43" s="1">
+        <v>42</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s">
+        <v>162</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J44" s="5">
+        <v>43</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="2">
+        <v>9.99</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J45" s="1">
+        <v>44</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="2">
+        <v>11.99</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" t="s">
+        <v>162</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J46" s="5">
+        <v>45</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="2">
+        <v>15.99</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" t="s">
+        <v>162</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J47" s="1">
+        <v>46</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="2">
+        <v>14.99</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G48" t="s">
+        <v>162</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J48" s="5">
+        <v>47</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C49" s="2">
+        <v>14.99</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" t="s">
+        <v>162</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J49" s="1">
+        <v>48</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="2">
+        <v>11.99</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" t="s">
+        <v>162</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J50" s="5">
+        <v>49</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}"/>
+  <autoFilter ref="A1:K37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
+      <sortCondition ref="J1:J37"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="J2:J50">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -4834,16 +5445,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A83E87-90D2-4FFE-A6A7-E278883B4F92}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
-    <col min="5" max="12" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
+    <col min="5" max="12" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4881,7 +5492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4917,7 +5528,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4953,7 +5564,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -4989,7 +5600,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -5025,7 +5636,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -5061,7 +5672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -5097,7 +5708,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -5133,7 +5744,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -5169,7 +5780,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -5205,7 +5816,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -5241,7 +5852,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -5277,7 +5888,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -5313,7 +5924,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -5349,7 +5960,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -5385,7 +5996,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -5421,7 +6032,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -5457,7 +6068,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -5493,7 +6104,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
@@ -5529,7 +6140,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -5565,7 +6176,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
@@ -5601,7 +6212,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>1</v>
       </c>
@@ -5637,7 +6248,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
@@ -5673,7 +6284,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>1</v>
       </c>
@@ -5709,7 +6320,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
@@ -5745,7 +6356,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -5781,7 +6392,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -5817,7 +6428,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -5853,7 +6464,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -5889,7 +6500,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
@@ -5925,7 +6536,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
@@ -5961,7 +6572,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -5997,7 +6608,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -6033,7 +6644,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -6069,7 +6680,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -6105,7 +6716,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
@@ -6141,7 +6752,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="80.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -6177,15 +6788,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:L37" xr:uid="{C7F39E25-AA98-49CF-A972-006AFA0C8782}">
     <filterColumn colId="1">

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssamu\Desktop\Coding\alas-catalogo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C495729A-4A31-4D66-ADC2-09053E8B50DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C13592A-C1F6-4759-B863-29E2C02F8A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3EE13C3-C0F4-4078-9950-3F2F6B639038}"/>
   </bookViews>
